--- a/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
+++ b/src/test/resources/testdataCRM/ClientsDataExcel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\main\resources\testdataCRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\Automation\Automationorangehrmlive\src\test\resources\testdataCRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A01688F6-2BB2-4204-9B62-1E0FEB77ECEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE205F0-235C-471C-9D49-A1647283D8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1C70021-F00B-48AF-8A5C-B0F1B7222A21}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>TESTCASENAME</t>
   </si>
   <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
     <t>PASSWORD</t>
   </si>
   <si>
@@ -59,13 +56,19 @@
     <t>testSignInData</t>
   </si>
   <si>
-    <t>admin@example.com</t>
-  </si>
-  <si>
     <t>T+wyT5u9cOelDJbBWNgxLw==</t>
   </si>
   <si>
-    <t>client@example.com</t>
+    <t>xDJm/aZjI0DLW6LEdeeL/Q==</t>
+  </si>
+  <si>
+    <t>USERNAME</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Client</t>
   </si>
 </sst>
 </file>
@@ -505,48 +508,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{DD399C4B-1694-4CEB-8894-974558E9E35A}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{1769E399-E4FF-4A87-8064-08CAC20FAB25}"/>
+    <hyperlink ref="B2" r:id="rId1" display="admin@example.com" xr:uid="{DD399C4B-1694-4CEB-8894-974558E9E35A}"/>
+    <hyperlink ref="B3" r:id="rId2" display="client@example.com" xr:uid="{1769E399-E4FF-4A87-8064-08CAC20FAB25}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
